--- a/artfynd/Söderbyskogens naturreservat artfynd.xlsx
+++ b/artfynd/Söderbyskogens naturreservat artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY94"/>
+  <dimension ref="A1:AZ94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85932424</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73591980</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73117428</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73117402</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73591083</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,6 +1343,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559985</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559987</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1507,6 +1547,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559989</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1604,6 +1649,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559990</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1701,6 +1751,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559991</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1798,6 +1853,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559992</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1895,6 +1955,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559993</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1992,6 +2057,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559999</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2092,6 +2162,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64286511</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2189,6 +2264,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64504155</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2286,6 +2366,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64714552</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2383,6 +2468,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64714554</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2484,6 +2574,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73116911</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2585,6 +2680,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73116968</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2691,6 +2791,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73117171</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2806,6 +2911,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102951830</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2911,6 +3021,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73116979</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3016,6 +3131,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73117141</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3113,6 +3233,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559955</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3210,6 +3335,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559959</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3307,6 +3437,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559961</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3430,6 +3565,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64282562</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3553,6 +3693,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64283238</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3653,6 +3798,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73117154</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3758,6 +3908,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73117447</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3858,6 +4013,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73591571</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3958,6 +4118,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73591825</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4068,6 +4233,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106813018</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4182,6 +4352,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106813021</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4279,6 +4454,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58560000</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4384,6 +4564,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73117062</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4489,6 +4674,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73117068</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4594,6 +4784,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73591793</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4696,6 +4891,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559965</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4808,6 +5008,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73591521</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4920,6 +5125,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73116954</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5036,6 +5246,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73117108</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5133,6 +5348,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559956</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5230,6 +5450,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559964</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5327,6 +5552,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559977</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5424,6 +5654,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559981</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5521,6 +5756,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559982</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5618,6 +5858,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559983</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5715,6 +5960,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559984</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5812,6 +6062,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559994</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5909,6 +6164,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559997</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6016,6 +6276,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73116887</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6123,6 +6388,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73116908</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6223,6 +6493,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64714543</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6340,6 +6615,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72968649</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6452,6 +6732,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73117025</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6557,6 +6842,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64284783</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6662,6 +6952,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64285934</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6759,6 +7054,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559972</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6856,6 +7156,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559973</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6953,6 +7258,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559978</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7058,6 +7368,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64714551</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7159,6 +7474,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73117199</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7265,6 +7585,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73591143</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7380,6 +7705,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95020302</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7488,6 +7818,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112647434</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7598,6 +7933,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112681497</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7695,6 +8035,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559979</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7792,6 +8137,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559986</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7904,6 +8254,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64399194</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8016,6 +8371,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64399201</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8128,6 +8488,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64504156</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8228,6 +8593,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73117184</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8328,6 +8698,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73591256</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8433,6 +8808,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73117208</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8543,6 +8923,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120428789</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8656,6 +9041,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67766473</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8769,6 +9159,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67766474</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8882,6 +9277,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73591340</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8995,6 +9395,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73591434</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9105,6 +9510,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120428745</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9217,6 +9627,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73117236</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9329,6 +9744,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73117293</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9426,6 +9846,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58559952</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9533,6 +9958,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73117369</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9650,6 +10080,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72968645</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9767,6 +10202,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72968647</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9884,6 +10324,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72968648</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9998,6 +10443,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105319909</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10098,6 +10548,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64287734</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10208,6 +10663,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112682227</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10313,6 +10773,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73117262</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10436,8 +10901,108 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95020335</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>